--- a/testmgmt/generated/MVP2_Testcases.xlsx
+++ b/testmgmt/generated/MVP2_Testcases.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -444,9 +444,10 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,6 +511,11 @@
           <t>Governance Status</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -562,6 +568,11 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
         </is>
       </c>
     </row>
@@ -633,6 +644,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -694,6 +710,11 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
         </is>
       </c>
     </row>
@@ -765,6 +786,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -828,6 +854,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,6 +920,11 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
         </is>
       </c>
     </row>
@@ -960,6 +996,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1021,6 +1062,11 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1138,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1153,6 +1204,1645 @@
       <c r="L11" t="inlineStr">
         <is>
           <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MVP2-HISTORICAL (frozen baseline 33b9946)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>REQ-REG-02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Registration rejects mismatched Password/Confirm password</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REG-02 (Approved SRS): "The password and confirmation password do not match." is shown and no account is created.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>The real registration page is reachable.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Register' link.
+3. Enter valid, unique First name, Last name, and Email.
+4. Enter a valid Password.
+5. Enter a different value in Confirm password.
+6. Submit the registration form.
+7. Observe the resulting page for the password-mismatch message.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-02-01</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-REG-02-MISMATCH</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>REQ-REG-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Registration rejects a malformed email</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REG-03 (Approved SRS): "Wrong email" is shown and no account is created.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The real registration page is reachable.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Register' link.
+3. Enter valid First name, Last name.
+4. Enter a malformed email value (not-an-email).
+5. Enter matching, valid Password and Confirm password.
+6. Submit the registration form.
+7. Observe the resulting page for the email-format message.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-03-01</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-REG-03-MALFORMED-EMAIL</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>REQ-REG-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Successful registration authenticates the user automatically</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REG-05 (Approved SRS): the resulting page shows an authenticated state without a separate login step.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The real registration page is reachable.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Register' link.
+3. Enter a genuinely unique, synthetic First name, Last name, Email (timestamp-suffixed to guarantee uniqueness), Password, and Confirm password.
+4. Submit the registration form.
+5. Observe the resulting page for an authenticated-state indicator (e.g. the account/logout link replacing 'Register'/'Log in').</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-REG-05-AUTO-LOGIN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-REG-04-DUPLICATE-EMAIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>REQ-REG-04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Registration rejects a duplicate email</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REG-04 (Approved SRS): "The specified email already exists" is shown and no second account is created.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN already exists.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Register' link.
+3. Enter valid First name, Last name, matching Password/Confirm password.
+4. Enter the Email already used by the real account from ENH02-TC-REQ-REG-05-AUTO-LOGIN.
+5. Submit the registration form.
+6. Observe the resulting page for the duplicate-email message.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-04-01</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-REG-04-DUPLICATE-EMAIL</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-AUTH-01-VALID-LOGIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Login succeeds with correct, registered credentials</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-01 (Approved SRS): an authenticated state is reached.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN already exists and is logged out.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Log in' link.
+3. Enter the real account's Email and Password.
+4. Submit the login form.
+5. Observe the resulting page for an authenticated-state indicator.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-AUTH-01-VALID-LOGIN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-AUTH-02-WRONG-PASSWORD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Login rejects an incorrect password with a generic message</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-02 (Approved SRS): "The credentials provided are incorrect" is shown and no session is created.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN already exists.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Log in' link.
+3. Enter the real account's registered Email with an incorrect password.
+4. Submit the login form.
+5. Observe the resulting page for the generic rejection message.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-AUTH-02-WRONG-PASSWORD</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-AUTH-03-RELOGIN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A just-registered account can log in again after logout</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-03 (Approved SRS): login succeeds.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN exists (already authenticated from registration).</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. From the authenticated state left by registration, select 'Log out'.
+2. Select the 'Log in' link.
+3. Enter the real account's Email and Password.
+4. Submit the login form.
+5. Observe the resulting page for an authenticated-state indicator.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-AUTH-03-RELOGIN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-PWR-01-RECOVERY-UI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>REQ-PWR-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Password recovery request accepted at the UI level</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PWR-01 (Approved SRS): the UI shows acceptance and no error. (UI-acceptance scope only -- email delivery/reset-token validity are explicitly out of MVP2 acceptance scope, per SRS sec. 6.3.)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN exists.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the password-recovery page.
+2. Enter the real account's registered Email.
+3. Submit the recovery request.
+4. Observe the resulting page for the acceptance message and absence of an error.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-PWR-01-RECOVERY-UI</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-01-VALID-KEYWORD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Search returns matching product results for a valid keyword</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-01 (Approved SRS): at least one result renders.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The real search page is reachable.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Enter a real, known keyword (e.g. 'book') in the search box.
+3. Submit the search.
+4. Observe the results page for at least one rendered result.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-01-01</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-SRCH-01-VALID-KEYWORD</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-SRCH-02-NO-RESULTS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Search shows an explicit no-results message for a nonsense keyword</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-SRCH-02 (Approved SRS): "No products were found that matched your criteria." is shown, zero results render.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The real search page is reachable.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Enter a nonsense keyword guaranteed to match nothing.
+3. Submit the search.
+4. Observe the results page for the explicit no-results message.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ENH02-TD-SRCH-02-01</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-SRCH-02-NO-RESULTS</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-BRW-01-CATEGORY-GRID</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>REQ-BRW-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Selecting a top-level category renders a product grid</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>REQ-BRW-01 (Approved SRS): a product grid renders.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The real main navigation is reachable.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the home page.
+2. Select the 'Books' top-level category link from the main navigation.
+3. Observe the resulting page for a rendered product grid.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-BRW-01-CATEGORY-GRID</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CFG-01-MANDATORY-ATTRIBUTE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>REQ-CFG-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Add to Cart blocked when a mandatory configurable attribute is unselected</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CFG-01 (Approved SRS): a message names the missing attribute ("Please select HDD") and the cart is unchanged.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>A real configurable product page ('Build your own computer') with a mandatory, no-default attribute (HDD) is reachable.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the 'Build your own computer' product page.
+2. Leave the mandatory HDD attribute unselected.
+3. Select Add to Cart.
+4. Observe the resulting message for a specific reference to the missing attribute.
+5. Confirm the cart remains unchanged.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CFG-01-MANDATORY-ATTRIBUTE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CART-01-ADD-CONFIRMATION</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>REQ-CART-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Add to Cart confirms the addition</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-01 (Approved SRS): a success notice appears and cart count increments.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>A real product detail page is reachable.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to a real product detail page ('3rd Album').
+2. Select Add to Cart.
+3. Observe the success notice.
+4. Observe the cart-count indicator incrementing.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CART-01-ADD-CONFIRMATION</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CART-02-QUANTITY-UPDATE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>REQ-CART-02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Updating quantity recalculates subtotal and total</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-02 (Approved SRS): subtotal = unit price x 3 and the cart total reflects it.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>A cart with one real item exists (chained from REQ-CART-01's own add step).</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. With one item in the cart, navigate to the cart page.
+2. Change the line item's quantity from 1 to 3.
+3. Select 'Update shopping cart'.
+4. Observe the line subtotal and cart total for proportional recalculation.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CART-02-QUANTITY-UPDATE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CART-03-ZERO-QUANTITY-REMOVES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>REQ-CART-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Setting quantity to 0 removes the line item without a prompt</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-03 (Approved SRS): the line item no longer appears; no prompt is shown.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>A cart with one real item exists.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. With one item in the cart, navigate to the cart page.
+2. Set the line item's quantity to 0.
+3. Select 'Update shopping cart'.
+4. Observe that the line item no longer appears and no confirmation dialog was shown.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CART-03-ZERO-QUANTITY-REMOVES</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CART-04-EMPTY-CART-STATE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>REQ-CART-04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Empty cart shows an empty-state message and blocks checkout</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-04 (Approved SRS): "Your Shopping Cart is empty!" shows and checkout cannot proceed.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>The cart is empty (chained after REQ-CART-03's own removal step, or a fresh session).</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. With an empty cart, navigate to the cart page.
+2. Observe the empty-state message.
+3. Confirm no active checkout action is available.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CART-04-EMPTY-CART-STATE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-CART-05-PERSISTENCE-ACROSS-LOGIN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>REQ-CART-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Anonymous cart item persists after logging in</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CART-05 (Approved SRS): the anonymously added item remains visible after login.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN exists.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. As an anonymous session, add a real product to the cart.
+2. Log in with the real account's Email/Password, same browser session.
+3. Navigate to the cart page.
+4. Observe that the previously added item is still present.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-CART-05-PERSISTENCE-ACROSS-LOGIN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-WISH-01-ADD-TO-WISHLIST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>REQ-WISH-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Add to Wishlist on an eligible product detail page</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>REQ-WISH-01 (Approved SRS): a wishlist-add confirmation shows.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>A real, eligible product detail page (Digital Downloads: '3rd Album') exposing Add to Wishlist is reachable.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the '3rd Album' product detail page.
+2. Select 'Add to wishlist'.
+3. Observe the wishlist-add confirmation.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-WISH-01-ADD-TO-WISHLIST</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-WISH-02-WISHLIST-PAGE-REFLECTS-ITEM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>REQ-WISH-02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wishlist page reflects a just-added item with price and actions</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>REQ-WISH-02 (Approved SRS): the item appears with price and available actions.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>An item was just added to the wishlist (chained from REQ-WISH-01).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. After adding an item to the wishlist, navigate to the wishlist page.
+2. Observe the item's presence, price, and available actions (Remove, Add to cart).</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-WISH-02-WISHLIST-PAGE-REFLECTS-ITEM</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-WISH-03-SHAREABLE-URL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>REQ-WISH-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Anonymous wishlist displays a shareable URL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>REQ-WISH-03 (Approved SRS): a shareable URL is displayed.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>An anonymous session has items in its wishlist (chained from REQ-WISH-01).</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. As an anonymous session with items in the wishlist, navigate to the wishlist page.
+2. Observe the page for a displayed shareable URL.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-WISH-03-SHAREABLE-URL</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-GCO-01-GUEST-CHECKOUT-INIT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>REQ-GCO-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Anonymous user initiates checkout via 'Checkout as Guest'</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GCO-01 (Approved SRS): a working 'Checkout as Guest' path proceeds without login/registration.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>An anonymous session has a real item in the cart.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. With a real item in the cart, accept the Terms of Service checkbox.
+2. Select 'Checkout'.
+3. On the guest-or-register interstitial, select 'Checkout as Guest'.
+4. Observe that the checkout page loads, still anonymous (no account created).</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-GCO-01-GUEST-CHECKOUT-INIT</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-GCO-02-GUEST-STEP-SEQUENCE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>REQ-GCO-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Guest checkout presents the same Billing Address step as authenticated checkout</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GCO-02 (Approved SRS): the same named 'Billing address' step structure appears as for an authenticated user.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>A guest checkout session has just been initiated (chained from REQ-GCO-01).</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Having reached the guest checkout page, observe the first step's heading/content.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-GCO-02-GUEST-STEP-SEQUENCE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-03-ADDRESS-FORM-VALIDATION</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>REQ-ACO-03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Billing address form blocks progression when required fields are blank</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ACO-03 (Approved SRS): progression to the next step is blocked when required fields are blank.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>A guest checkout session has reached the Billing Address step (chained from REQ-GCO-01/02).</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. At the Billing Address step, leave the required fields (First name, Last name, Email, Country, City, Address 1, Zip/postal code, Phone number) blank.
+2. Attempt to continue to the next step.
+3. Observe that progression is blocked.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-03-ADDRESS-FORM-VALIDATION</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACCT-01-ACCOUNT-PAGES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>REQ-ACCT-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Authenticated customer can access Customer Info, Addresses, and Orders</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ACCT-01 (Approved SRS): each of the three account pages loads without redirect to login.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN exists and is authenticated.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. While authenticated, navigate to the Customer Info page.
+2. Navigate to the Addresses page.
+3. Navigate to the Orders page.
+4. Observe that each page loads without redirecting to the login page.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ENH02-TD-REG-05-01</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACCT-01-ACCOUNT-PAGES</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>
       </c>
     </row>
@@ -1167,7 +2857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1270,6 +2960,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Post-MVP2 Enhancement 02 added a new, explicit, business-level testcase corpus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>(rows marked Origin=POST-MVP2 ENHANCEMENT 02) for 25 Approved SRS requirements,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>grounded directly in each requirement's own Statement/Acceptance Criteria text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>None of the 10 historical MVP2 testcases above were modified. Enhancement 02's</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>own 'Execution Status' reflects real, live Playwright execution logs (see</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>docs/claude-execution-reports/ENHANCEMENT-02/ for the full report).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testmgmt/generated/MVP2_Testcases.xlsx
+++ b/testmgmt/generated/MVP2_Testcases.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>ERROR/PASS</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2841,6 +2841,213 @@
         </is>
       </c>
       <c r="M35" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01, REQ-SHIP-01, REQ-PAY-01, REQ-PAY-02, REQ-PAY-03, REQ-CONF-01, REQ-CONF-02</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Authenticated checkout proceeds through all named steps to a completed order</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ACO-01: the order completes and the Order Completed page renders. REQ-SHIP-01/REQ-PAY-01: each respective step presents more than one real, selectable option. REQ-PAY-03: the Payment Info step renders zero real input/select/textarea fields for Cash On Delivery. REQ-PAY-02: the confirmed total reflects the payment method's additional fee. REQ-CONF-01: a real order number is shown. REQ-CONF-02: Total == Sub-Total + Shipping + Payment method additional fee + Tax (computed check, never a hard-coded literal per SRS sec. 10).</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>The real account created by ENH02-TC-REQ-REG-05-AUTO-LOGIN exists and is authenticated.
+A real, physical (non-digital-download) product is reachable ('Computing and Internet' book) -- real evidence, this task: a cart containing only digital-download items skips the Shipping Address/Shipping Method steps entirely, so a physical item is a genuine precondition, not an implementation detail.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Add the real 'Computing and Internet' product to the cart.
+2. Accept the Terms of Service checkbox and select 'Checkout' (already authenticated: no guest interstitial appears).
+3. At the Billing Address step, enter First name, Last name, Email, Country (United States), State, City, Address 1, Zip/postal code, Phone number, then Continue.
+4. At the Shipping Address step, accept the pre-selected address (the just-entered Billing Address, auto-saved and offered as the default shipping address), then Continue.
+5. At the Shipping Method step, observe that multiple real shipping options are presented; select the default option and Continue.
+6. At the Payment Method step, observe that multiple real payment options are presented; select Cash On Delivery and Continue.
+7. At the Payment Info step, observe that Cash On Delivery presents no payment-detail form, then Continue.
+8. At the Confirm Order step, observe the real Sub-Total/Shipping/Payment method additional fee/Tax/Total breakdown.
+9. Select 'Confirm' to submit the order.
+10. Observe the Order Completed page for the success message and a real, unique order number.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ENH02-TD-ACO-01-01</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ERROR/PASS</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-OHIST-01-ORDER-APPEARS-IN-HISTORY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>REQ-OHIST-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A just-completed order appears in the customer's Order History</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>REQ-OHIST-01 (Approved SRS): the completed order appears in Order History.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>The real order from ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION has just completed, and its real order number is known.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to the Order History page (Orders, under My account).
+2. Observe that the real order number just obtained is listed.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-OHIST-01-ORDER-APPEARS-IN-HISTORY</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-02-SAVED-ADDRESS-REUSE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>REQ-ACO-02</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A repeat checkout offers the previously-saved address via selection</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>REQ-ACO-02 (Approved SRS): the address-selection control offers the previously-saved address as an option, in addition to 'New Address'.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>The real account has at least one previously-saved address (from ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION's real Billing Address submission).</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Add a real product to the cart.
+2. Accept the Terms of Service checkbox and select 'Checkout'.
+3. At the Billing Address step, observe the address-selection control.
+4. Do not proceed further (this testcase does not create a second order).</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-02-SAVED-ADDRESS-REUSE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>POST-MVP2 ENHANCEMENT 02</t>
         </is>

--- a/testmgmt/generated/MVP2_Testcases.xlsx
+++ b/testmgmt/generated/MVP2_Testcases.xlsx
@@ -1558,7 +1558,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ERROR/PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ERROR/PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">

--- a/testmgmt/generated/MVP2_Testcases.xlsx
+++ b/testmgmt/generated/MVP2_Testcases.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3053,6 +3053,84 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>REQ-GCO-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Guest checkout culminates in order confirmation and a generated order number</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>REQ-GCO-03 (Approved SRS): the guest checkout culminates in a real order confirmation and a real, generated order number, via the same named step sequence and mechanism already evidenced for the authenticated path (REQ-ACO-01) -- without any authentication or account creation at any point.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>The session is genuinely anonymous -- no login, no registration, no reuse of the existing shared authenticated account or its saved address.
+A real, physical (non-digital-download) product is reachable ('Computing and Internet' book) -- real evidence (this task and the prior Enhancement-02 closure): a cart containing only digital-download items skips the Shipping Address/Shipping Method steps entirely, which would not faithfully mirror REQ-ACO-01's own 6-named-step mechanism this requirement must be 'consistent with'.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. As an anonymous session, add the real 'Computing and Internet' product to the cart.
+2. Accept the Terms of Service checkbox and select 'Checkout'.
+3. On the guest-or-register interstitial, select 'Checkout as Guest' (remain anonymous -- no account created).
+4. At the Billing Address step, enter First name, Last name, Email, Country (United States), State, City, Address 1, Zip/postal code, Phone number, then Continue.
+5. At the Shipping Address step, accept the pre-selected (auto-saved) shipping address, then Continue.
+6. At the Shipping Method step, observe multiple real shipping options are presented; select the default option and Continue.
+7. At the Payment Method step, observe multiple real payment options are presented; select Cash On Delivery and Continue.
+8. At the Payment Info step, observe that Cash On Delivery presents no payment-detail form, then Continue.
+9. At the Confirm Order step, observe the real Sub-Total/Shipping/Payment method additional fee/Tax/Total breakdown.
+10. Select 'Confirm' to submit the order.
+11. Observe the Order Completed page for the success message and a real, unique order number.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ENH02-TD-GCO-03-01</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>POST-MVP2 ENHANCEMENT 02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
